--- a/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>TFC</t>
   </si>
@@ -656,105 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24456000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16637000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13774000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15548000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9409000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8120000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7374000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7066000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6327000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6142000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6507000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6917000</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,9 +797,12 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -830,9 +839,12 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,9 +941,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,48 +983,54 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-527000</v>
+      </c>
+      <c r="E15" s="3">
         <v>-583000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-574000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-685000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-164000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-131000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-142000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-150000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-105000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-91000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-106000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-110000</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11965000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3098000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-45000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1722000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2711000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2004000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1386000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1317000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1163000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1019000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1483000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2117000</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12491000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13539000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13819000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13826000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6698000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6116000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5988000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5749000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5164000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5123000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5024000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4800000</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,86 +1145,93 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12676000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5870000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5826000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8353000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2679000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2056000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2662000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2249000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2247000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1996000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1741000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2008000</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1030000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9035000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9377000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7081000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4649000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4615000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3876000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4055000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3378000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3551000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3704000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3183000</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1229,87 +1268,96 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7669000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7993000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5473000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4019000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4060000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3326000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3500000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2917000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3127000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3283000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2792000</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>862000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1402000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1556000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>981000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>782000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>830000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>954000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1058000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>794000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>921000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1553000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>764000</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1047000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6267000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6437000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4492000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3237000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3230000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2372000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2442000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2123000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2206000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1730000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2028000</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1452000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5927000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6033000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4184000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3028000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3036000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2177000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2259000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1936000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1983000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1563000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1916000</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1478,18 +1538,18 @@
       <c r="F29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>27000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>43000</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12676000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5870000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5826000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8353000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2679000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2056000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2662000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2249000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2247000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1996000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1741000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2008000</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1452000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5927000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6033000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4184000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3028000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3063000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2220000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2259000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1936000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1983000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1563000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1916000</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1452000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5927000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6033000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4184000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3028000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3063000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2220000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2259000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1936000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1983000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1563000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1916000</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,86 +1900,93 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5072000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5379000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5085000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5029000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4084000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2753000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2243000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1897000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2123000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1639000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1565000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2011000</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>33233000</v>
+      </c>
+      <c r="E42" s="3">
         <v>24812000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23661000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23457000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24184000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1128000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>513000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2089000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1646000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1294000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1418000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2519000</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1931,9 +2023,12 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1970,9 +2065,12 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2009,9 +2107,12 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2048,9 +2149,12 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2087,87 +2191,96 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4439000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4798000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5203000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5535000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2118000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2055000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2107000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2007000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3654000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3738000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3776000</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27439000</v>
+      </c>
+      <c r="E49" s="3">
         <v>34443000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32139000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>29454000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29926000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11684000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11385000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11544000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10114000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8723000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8999000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8777000</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6563000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4539000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
         <v>4358000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3579000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>90000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>75000</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>535349000</v>
+      </c>
+      <c r="E54" s="3">
         <v>555255000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>541241000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>509228000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>473078000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>225697000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>221642000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>219276000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>209947000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>186834000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>183010000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>184499000</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,47 +2524,51 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18114000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16080000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12447000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9081000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8737000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5332000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5838000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5745000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6066000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12514000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14037000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8223000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2469,30 +2602,33 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1408000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1545000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1600000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1896000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2121000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2508,12 +2644,15 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2550,87 +2689,96 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38917000</v>
+      </c>
+      <c r="E61" s="3">
         <v>43201000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35050000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38583000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37198000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21960000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21168000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17847000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18037000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23312000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21493000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19114000</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>230000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>573000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1012000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>101000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>152000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>55000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>262000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>153000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>476248000</v>
+      </c>
+      <c r="E66" s="3">
         <v>494741000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>471970000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>438421000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>406694000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>195575000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>191994000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189395000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>182641000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>162545000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>160251000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>163341000</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2892,13 +3059,13 @@
         <v>6673000</v>
       </c>
       <c r="F70" s="3">
+        <v>6673000</v>
+      </c>
+      <c r="G70" s="3">
         <v>8048000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>5102000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>3053000</v>
       </c>
       <c r="I70" s="3">
         <v>3053000</v>
@@ -2907,20 +3074,23 @@
         <v>3053000</v>
       </c>
       <c r="K70" s="3">
-        <v>2603000</v>
+        <v>3053000</v>
       </c>
       <c r="L70" s="3">
         <v>2603000</v>
       </c>
       <c r="M70" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="N70" s="3">
         <v>5206000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2116000</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22088000</v>
+      </c>
+      <c r="E72" s="3">
         <v>26264000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22998000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19455000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19806000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18118000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16259000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14809000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13464000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12317000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11044000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10129000</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52428000</v>
+      </c>
+      <c r="E76" s="3">
         <v>53841000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62598000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>62759000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61282000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27069000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26595000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26828000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24703000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21686000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17553000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19042000</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1452000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5927000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6033000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4184000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3028000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3063000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2220000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2259000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1936000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1983000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1563000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1916000</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1215000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1366000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1384000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1608000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>630000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>555000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>550000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>555000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>461000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>424000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>421000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>391000</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8631000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11081000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7892000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7437000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1520000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4349000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4635000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3115000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3131000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3210000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5308000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3714000</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,23 +3801,24 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-564000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-442000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-815000</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
@@ -3614,15 +3834,18 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-145000</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>22858000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29972000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32056000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43652000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>8348000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4963000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5410000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-976000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1849000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4015000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7047000</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3131000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2989000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2852000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2725000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1459000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1378000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1179000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1092000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-937000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-814000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-912000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-564000</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,48 +4152,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22266000</v>
+      </c>
+      <c r="E100" s="3">
         <v>20017000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>25591000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36018000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5353000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1502000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-549000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1882000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>104000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>965000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1973000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2796000</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3988,46 +4236,52 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9223000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1126000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1427000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-197000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15221000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>888000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1324000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>257000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1386000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>160000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-874000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-537000</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>TFC</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24456000</v>
+        <v>21281000</v>
       </c>
       <c r="E8" s="3">
-        <v>16637000</v>
+        <v>22258000</v>
       </c>
       <c r="F8" s="3">
-        <v>13774000</v>
+        <v>23109000</v>
       </c>
       <c r="G8" s="3">
-        <v>15548000</v>
+        <v>20370000</v>
       </c>
       <c r="H8" s="3">
-        <v>9409000</v>
+        <v>11953000</v>
       </c>
       <c r="I8" s="3">
-        <v>8120000</v>
+        <v>10992000</v>
       </c>
       <c r="J8" s="3">
-        <v>7374000</v>
+        <v>10770000</v>
       </c>
       <c r="K8" s="3">
         <v>7066000</v>
@@ -806,26 +806,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>21281000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>22258000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>23109000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20370000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>11953000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>10992000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>10770000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>6453000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>474000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>860000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>146000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>507000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-527000</v>
+        <v>1040000</v>
       </c>
       <c r="E15" s="3">
-        <v>-583000</v>
+        <v>1182000</v>
       </c>
       <c r="F15" s="3">
-        <v>-574000</v>
+        <v>1194000</v>
       </c>
       <c r="G15" s="3">
-        <v>-685000</v>
+        <v>1350000</v>
       </c>
       <c r="H15" s="3">
-        <v>-164000</v>
+        <v>494000</v>
       </c>
       <c r="I15" s="3">
-        <v>-131000</v>
+        <v>435000</v>
       </c>
       <c r="J15" s="3">
-        <v>-142000</v>
+        <v>430000</v>
       </c>
       <c r="K15" s="3">
         <v>-150000</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11965000</v>
+        <v>13662000</v>
       </c>
       <c r="E17" s="3">
-        <v>3098000</v>
+        <v>13349000</v>
       </c>
       <c r="F17" s="3">
-        <v>-45000</v>
+        <v>13583000</v>
       </c>
       <c r="G17" s="3">
-        <v>1722000</v>
+        <v>13227000</v>
       </c>
       <c r="H17" s="3">
-        <v>2711000</v>
+        <v>7329000</v>
       </c>
       <c r="I17" s="3">
-        <v>2004000</v>
+        <v>6521000</v>
       </c>
       <c r="J17" s="3">
-        <v>1386000</v>
+        <v>6642000</v>
       </c>
       <c r="K17" s="3">
         <v>1317000</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12491000</v>
+        <v>7619000</v>
       </c>
       <c r="E18" s="3">
-        <v>13539000</v>
+        <v>8909000</v>
       </c>
       <c r="F18" s="3">
-        <v>13819000</v>
+        <v>9526000</v>
       </c>
       <c r="G18" s="3">
-        <v>13826000</v>
+        <v>7143000</v>
       </c>
       <c r="H18" s="3">
-        <v>6698000</v>
+        <v>4624000</v>
       </c>
       <c r="I18" s="3">
-        <v>6116000</v>
+        <v>4471000</v>
       </c>
       <c r="J18" s="3">
-        <v>5988000</v>
+        <v>4128000</v>
       </c>
       <c r="K18" s="3">
         <v>5749000</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12676000</v>
+        <v>1351000</v>
       </c>
       <c r="E20" s="3">
-        <v>-5870000</v>
+        <v>766000</v>
       </c>
       <c r="F20" s="3">
-        <v>-5826000</v>
+        <v>711000</v>
       </c>
       <c r="G20" s="3">
-        <v>-8353000</v>
+        <v>810000</v>
       </c>
       <c r="H20" s="3">
-        <v>-2679000</v>
+        <v>245000</v>
       </c>
       <c r="I20" s="3">
-        <v>-2056000</v>
+        <v>265000</v>
       </c>
       <c r="J20" s="3">
-        <v>-2662000</v>
+        <v>295000</v>
       </c>
       <c r="K20" s="3">
         <v>-2249000</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1030000</v>
+        <v>7308000</v>
       </c>
       <c r="E21" s="3">
-        <v>9035000</v>
+        <v>9325000</v>
       </c>
       <c r="F21" s="3">
-        <v>9377000</v>
+        <v>10009000</v>
       </c>
       <c r="G21" s="3">
-        <v>7081000</v>
+        <v>7683000</v>
       </c>
       <c r="H21" s="3">
-        <v>4649000</v>
+        <v>4873000</v>
       </c>
       <c r="I21" s="3">
-        <v>4615000</v>
+        <v>4641000</v>
       </c>
       <c r="J21" s="3">
-        <v>3876000</v>
+        <v>4263000</v>
       </c>
       <c r="K21" s="3">
         <v>4055000</v>
@@ -1235,26 +1235,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1335,10 +1335,10 @@
         <v>782000</v>
       </c>
       <c r="I24" s="3">
-        <v>830000</v>
+        <v>803000</v>
       </c>
       <c r="J24" s="3">
-        <v>954000</v>
+        <v>911000</v>
       </c>
       <c r="K24" s="3">
         <v>1058000</v>
@@ -1419,10 +1419,10 @@
         <v>3237000</v>
       </c>
       <c r="I26" s="3">
-        <v>3230000</v>
+        <v>3257000</v>
       </c>
       <c r="J26" s="3">
-        <v>2372000</v>
+        <v>2415000</v>
       </c>
       <c r="K26" s="3">
         <v>2442000</v>
@@ -1461,10 +1461,10 @@
         <v>3028000</v>
       </c>
       <c r="I27" s="3">
-        <v>3036000</v>
+        <v>3063000</v>
       </c>
       <c r="J27" s="3">
-        <v>2177000</v>
+        <v>2220000</v>
       </c>
       <c r="K27" s="3">
         <v>2259000</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12676000</v>
+        <v>-1351000</v>
       </c>
       <c r="E32" s="3">
-        <v>5870000</v>
+        <v>-766000</v>
       </c>
       <c r="F32" s="3">
-        <v>5826000</v>
+        <v>-711000</v>
       </c>
       <c r="G32" s="3">
-        <v>8353000</v>
+        <v>-810000</v>
       </c>
       <c r="H32" s="3">
-        <v>2679000</v>
+        <v>-245000</v>
       </c>
       <c r="I32" s="3">
-        <v>2056000</v>
+        <v>-265000</v>
       </c>
       <c r="J32" s="3">
-        <v>2662000</v>
+        <v>-295000</v>
       </c>
       <c r="K32" s="3">
         <v>2249000</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1452000</v>
+        <v>-1091000</v>
       </c>
       <c r="E33" s="3">
-        <v>5927000</v>
+        <v>6260000</v>
       </c>
       <c r="F33" s="3">
-        <v>6033000</v>
+        <v>6440000</v>
       </c>
       <c r="G33" s="3">
-        <v>4184000</v>
+        <v>4482000</v>
       </c>
       <c r="H33" s="3">
-        <v>3028000</v>
+        <v>3224000</v>
       </c>
       <c r="I33" s="3">
-        <v>3063000</v>
+        <v>3237000</v>
       </c>
       <c r="J33" s="3">
-        <v>2220000</v>
+        <v>2394000</v>
       </c>
       <c r="K33" s="3">
         <v>2259000</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1452000</v>
+        <v>-1091000</v>
       </c>
       <c r="E35" s="3">
-        <v>5927000</v>
+        <v>6260000</v>
       </c>
       <c r="F35" s="3">
-        <v>6033000</v>
+        <v>6440000</v>
       </c>
       <c r="G35" s="3">
-        <v>4184000</v>
+        <v>4482000</v>
       </c>
       <c r="H35" s="3">
-        <v>3028000</v>
+        <v>3224000</v>
       </c>
       <c r="I35" s="3">
-        <v>3063000</v>
+        <v>3237000</v>
       </c>
       <c r="J35" s="3">
-        <v>2220000</v>
+        <v>2394000</v>
       </c>
       <c r="K35" s="3">
         <v>2259000</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5072000</v>
+        <v>30644000</v>
       </c>
       <c r="E41" s="3">
-        <v>5379000</v>
+        <v>21421000</v>
       </c>
       <c r="F41" s="3">
-        <v>5085000</v>
+        <v>20295000</v>
       </c>
       <c r="G41" s="3">
-        <v>5029000</v>
+        <v>18868000</v>
       </c>
       <c r="H41" s="3">
-        <v>4084000</v>
+        <v>19065000</v>
       </c>
       <c r="I41" s="3">
-        <v>2753000</v>
+        <v>3844000</v>
       </c>
       <c r="J41" s="3">
-        <v>2243000</v>
+        <v>2713000</v>
       </c>
       <c r="K41" s="3">
         <v>1897000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33233000</v>
+        <v>7661000</v>
       </c>
       <c r="E42" s="3">
-        <v>24812000</v>
+        <v>8770000</v>
       </c>
       <c r="F42" s="3">
-        <v>23661000</v>
+        <v>10821000</v>
       </c>
       <c r="G42" s="3">
-        <v>23457000</v>
+        <v>9454000</v>
       </c>
       <c r="H42" s="3">
-        <v>24184000</v>
+        <v>9203000</v>
       </c>
       <c r="I42" s="3">
-        <v>1128000</v>
+        <v>783000</v>
       </c>
       <c r="J42" s="3">
-        <v>513000</v>
+        <v>1076000</v>
       </c>
       <c r="K42" s="3">
         <v>2089000</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>2723000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>2682000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>2244000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>1833000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>2418000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>1116000</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>123000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>2345000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2265000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>1791000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>1934000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1807000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>745000</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>45840000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>37806000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>41166000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>39447000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>42243000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>8141000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>5315000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>130929000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>138516000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>162040000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>127527000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>81756000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>48804000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>47978000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2201,22 +2201,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4439000</v>
+        <v>6086000</v>
       </c>
       <c r="E48" s="3">
-        <v>4798000</v>
+        <v>6880000</v>
       </c>
       <c r="F48" s="3">
-        <v>3700000</v>
+        <v>6960000</v>
       </c>
       <c r="G48" s="3">
-        <v>5203000</v>
+        <v>7013000</v>
       </c>
       <c r="H48" s="3">
-        <v>5535000</v>
+        <v>7432000</v>
       </c>
       <c r="I48" s="3">
-        <v>2118000</v>
+        <v>3493000</v>
       </c>
       <c r="J48" s="3">
         <v>2055000</v>
@@ -2258,7 +2258,7 @@
         <v>29926000</v>
       </c>
       <c r="I49" s="3">
-        <v>11684000</v>
+        <v>11698000</v>
       </c>
       <c r="J49" s="3">
         <v>11385000</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6563000</v>
+        <v>14755000</v>
       </c>
       <c r="E52" s="3">
-        <v>4539000</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+        <v>12969000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>13858000</v>
       </c>
       <c r="G52" s="3">
-        <v>4358000</v>
+        <v>11888000</v>
       </c>
       <c r="H52" s="3">
-        <v>3579000</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>13428000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6106000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>12698000</v>
       </c>
       <c r="K52" s="3">
         <v>90000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>18114000</v>
+        <v>395865000</v>
       </c>
       <c r="E57" s="3">
-        <v>16080000</v>
+        <v>413495000</v>
       </c>
       <c r="F57" s="3">
-        <v>12447000</v>
+        <v>416488000</v>
       </c>
       <c r="G57" s="3">
-        <v>9081000</v>
+        <v>381077000</v>
       </c>
       <c r="H57" s="3">
-        <v>8737000</v>
+        <v>334727000</v>
       </c>
       <c r="I57" s="3">
-        <v>5332000</v>
+        <v>161199000</v>
       </c>
       <c r="J57" s="3">
-        <v>5838000</v>
+        <v>161989000</v>
       </c>
       <c r="K57" s="3">
         <v>5745000</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>27726000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>26393000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5878000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>6647000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>18974000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5425000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>5652000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2614,20 +2614,20 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1408000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1545000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1600000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1896000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2121000</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>423591000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>439888000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>422366000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>387724000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>353701000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>166624000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>167641000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>38917000</v>
+        <v>40025000</v>
       </c>
       <c r="E61" s="3">
-        <v>43201000</v>
+        <v>44748000</v>
       </c>
       <c r="F61" s="3">
-        <v>35050000</v>
+        <v>37513000</v>
       </c>
       <c r="G61" s="3">
-        <v>38583000</v>
+        <v>41493000</v>
       </c>
       <c r="H61" s="3">
-        <v>37198000</v>
+        <v>43070000</v>
       </c>
       <c r="I61" s="3">
-        <v>21960000</v>
+        <v>23709000</v>
       </c>
       <c r="J61" s="3">
-        <v>21168000</v>
+        <v>23648000</v>
       </c>
       <c r="K61" s="3">
         <v>17847000</v>
@@ -2740,26 +2740,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>11821000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9427000</v>
       </c>
       <c r="F62" s="3">
-        <v>230000</v>
+        <v>11121000</v>
       </c>
       <c r="G62" s="3">
-        <v>573000</v>
+        <v>7865000</v>
       </c>
       <c r="H62" s="3">
-        <v>1012000</v>
+        <v>8180000</v>
       </c>
       <c r="I62" s="3">
-        <v>101000</v>
+        <v>4699000</v>
       </c>
       <c r="J62" s="3">
-        <v>152000</v>
+        <v>119000</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>476248000</v>
+        <v>476096000</v>
       </c>
       <c r="E66" s="3">
-        <v>494741000</v>
+        <v>494718000</v>
       </c>
       <c r="F66" s="3">
         <v>471970000</v>
       </c>
       <c r="G66" s="3">
-        <v>438421000</v>
+        <v>438316000</v>
       </c>
       <c r="H66" s="3">
-        <v>406694000</v>
+        <v>406520000</v>
       </c>
       <c r="I66" s="3">
-        <v>195575000</v>
+        <v>195519000</v>
       </c>
       <c r="J66" s="3">
-        <v>191994000</v>
+        <v>191947000</v>
       </c>
       <c r="K66" s="3">
         <v>189395000</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1452000</v>
+        <v>-1091000</v>
       </c>
       <c r="E81" s="3">
-        <v>5927000</v>
+        <v>6260000</v>
       </c>
       <c r="F81" s="3">
-        <v>6033000</v>
+        <v>6440000</v>
       </c>
       <c r="G81" s="3">
-        <v>4184000</v>
+        <v>4482000</v>
       </c>
       <c r="H81" s="3">
-        <v>3028000</v>
+        <v>3224000</v>
       </c>
       <c r="I81" s="3">
-        <v>3063000</v>
+        <v>3237000</v>
       </c>
       <c r="J81" s="3">
-        <v>2220000</v>
+        <v>2394000</v>
       </c>
       <c r="K81" s="3">
         <v>2259000</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1215000</v>
+        <v>688000</v>
       </c>
       <c r="E83" s="3">
-        <v>1366000</v>
+        <v>783000</v>
       </c>
       <c r="F83" s="3">
-        <v>1384000</v>
+        <v>810000</v>
       </c>
       <c r="G83" s="3">
-        <v>1608000</v>
+        <v>923000</v>
       </c>
       <c r="H83" s="3">
-        <v>630000</v>
+        <v>466000</v>
       </c>
       <c r="I83" s="3">
-        <v>555000</v>
+        <v>424000</v>
       </c>
       <c r="J83" s="3">
-        <v>550000</v>
+        <v>408000</v>
       </c>
       <c r="K83" s="3">
         <v>555000</v>
@@ -3807,23 +3807,23 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-17000</v>
       </c>
       <c r="E91" s="3">
-        <v>-564000</v>
+        <v>-4673000</v>
       </c>
       <c r="F91" s="3">
-        <v>-442000</v>
+        <v>-1638000</v>
       </c>
       <c r="G91" s="3">
-        <v>-815000</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
+        <v>-3254000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-224000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-363000</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3131000</v>
+        <v>2770000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2989000</v>
+        <v>2656000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2852000</v>
+        <v>2485000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2725000</v>
+        <v>2424000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1459000</v>
+        <v>1309000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1378000</v>
+        <v>1169300</v>
       </c>
       <c r="J96" s="3">
-        <v>-1179000</v>
+        <v>1005000</v>
       </c>
       <c r="K96" s="3">
         <v>-1092000</v>
@@ -4203,26 +4203,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>TFC</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21281000</v>
+        <v>11408000</v>
       </c>
       <c r="E8" s="3">
-        <v>22258000</v>
+        <v>17913000</v>
       </c>
       <c r="F8" s="3">
+        <v>19196000</v>
+      </c>
+      <c r="G8" s="3">
         <v>23109000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20370000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11953000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10992000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10770000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7066000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6327000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6142000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6507000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6917000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,36 +806,39 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>21281000</v>
+        <v>11408000</v>
       </c>
       <c r="E10" s="3">
-        <v>22258000</v>
+        <v>17913000</v>
       </c>
       <c r="F10" s="3">
+        <v>19196000</v>
+      </c>
+      <c r="G10" s="3">
         <v>23109000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20370000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11953000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10992000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10770000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,36 +960,39 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6453000</v>
+        <v>120000</v>
       </c>
       <c r="E14" s="3">
-        <v>474000</v>
+        <v>6398000</v>
       </c>
       <c r="F14" s="3">
+        <v>466000</v>
+      </c>
+      <c r="G14" s="3">
         <v>822000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>860000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>360000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>146000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>507000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1040000</v>
+        <v>814000</v>
       </c>
       <c r="E15" s="3">
-        <v>1182000</v>
+        <v>908000</v>
       </c>
       <c r="F15" s="3">
+        <v>1054000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1194000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1350000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>494000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>435000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>430000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-150000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-105000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-91000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-106000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-110000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13662000</v>
+        <v>11200000</v>
       </c>
       <c r="E17" s="3">
-        <v>13349000</v>
+        <v>11061000</v>
       </c>
       <c r="F17" s="3">
+        <v>11063000</v>
+      </c>
+      <c r="G17" s="3">
         <v>13583000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13227000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7329000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6521000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6642000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1317000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1163000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1019000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1483000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2117000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7619000</v>
+        <v>208000</v>
       </c>
       <c r="E18" s="3">
-        <v>8909000</v>
+        <v>6852000</v>
       </c>
       <c r="F18" s="3">
+        <v>8133000</v>
+      </c>
+      <c r="G18" s="3">
         <v>9526000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7143000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4624000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4471000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4128000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5749000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5164000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5123000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5024000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4800000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1351000</v>
+        <v>689000</v>
       </c>
       <c r="E20" s="3">
-        <v>766000</v>
+        <v>1219000</v>
       </c>
       <c r="F20" s="3">
+        <v>638000</v>
+      </c>
+      <c r="G20" s="3">
         <v>711000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>810000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>245000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>265000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>295000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2249000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2247000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1996000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1741000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2008000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7308000</v>
+        <v>333000</v>
       </c>
       <c r="E21" s="3">
-        <v>9325000</v>
+        <v>6541000</v>
       </c>
       <c r="F21" s="3">
+        <v>8549000</v>
+      </c>
+      <c r="G21" s="3">
         <v>10009000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7683000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4873000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4641000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4263000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4055000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3378000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3551000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3704000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3183000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1295,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-185000</v>
+        <v>-601000</v>
       </c>
       <c r="E23" s="3">
-        <v>7669000</v>
+        <v>-765000</v>
       </c>
       <c r="F23" s="3">
+        <v>7029000</v>
+      </c>
+      <c r="G23" s="3">
         <v>7993000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5473000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4019000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4060000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3326000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3500000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2917000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3127000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3283000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2792000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>862000</v>
+        <v>-556000</v>
       </c>
       <c r="E24" s="3">
-        <v>1402000</v>
+        <v>738000</v>
       </c>
       <c r="F24" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="G24" s="3">
         <v>1556000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>981000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>782000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>803000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>911000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1058000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>794000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>921000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1553000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>764000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1047000</v>
+        <v>-45000</v>
       </c>
       <c r="E26" s="3">
-        <v>6267000</v>
+        <v>-1503000</v>
       </c>
       <c r="F26" s="3">
+        <v>5779000</v>
+      </c>
+      <c r="G26" s="3">
         <v>6437000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4492000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3237000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3257000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2415000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2442000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2123000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1730000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2028000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4469000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1452000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5927000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6033000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4184000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3028000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3063000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2259000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1936000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1983000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1563000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1916000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,20 +1580,23 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>4863000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>412000</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>481000</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1550,8 +1610,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1351000</v>
+        <v>-689000</v>
       </c>
       <c r="E32" s="3">
-        <v>-766000</v>
+        <v>-1219000</v>
       </c>
       <c r="F32" s="3">
+        <v>-638000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-711000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-810000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-245000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-265000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-295000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2249000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2247000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1996000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1741000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2008000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4818000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1091000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6260000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6440000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4482000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3224000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3237000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2394000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2259000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1936000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1983000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1563000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1916000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4818000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1091000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6260000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6440000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4482000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3224000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3237000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2394000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2259000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1936000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1983000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1563000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1916000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,118 +1986,125 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>30644000</v>
+        <v>39768000</v>
       </c>
       <c r="E41" s="3">
+        <v>30230000</v>
+      </c>
+      <c r="F41" s="3">
         <v>21421000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20295000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18868000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19065000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3844000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2713000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1897000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2123000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1639000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1565000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2011000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8616000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7661000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8770000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10821000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9454000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9203000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>783000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1076000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2089000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1646000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1294000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1418000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2519000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2723000</v>
+        <v>1904000</v>
       </c>
       <c r="E43" s="3">
+        <v>997000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2682000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2244000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1833000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2418000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1116000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2026,36 +2118,39 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E44" s="3">
         <v>57000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>62000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>51000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>52000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>123000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>63000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>57000</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2068,35 +2163,38 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2345000</v>
+        <v>2069000</v>
       </c>
       <c r="E45" s="3">
+        <v>9740000</v>
+      </c>
+      <c r="F45" s="3">
         <v>2265000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1791000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1934000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1807000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>745000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2110,36 +2208,39 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45840000</v>
+        <v>54854000</v>
       </c>
       <c r="E46" s="3">
+        <v>51048000</v>
+      </c>
+      <c r="F46" s="3">
         <v>37806000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41166000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39447000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>42243000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8141000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5315000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2152,36 +2253,39 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>130929000</v>
+        <v>128372000</v>
       </c>
       <c r="E47" s="3">
+        <v>130569000</v>
+      </c>
+      <c r="F47" s="3">
         <v>138516000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162040000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>127527000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>81756000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48804000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47978000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6086000</v>
+        <v>5592000</v>
       </c>
       <c r="E48" s="3">
+        <v>6002000</v>
+      </c>
+      <c r="F48" s="3">
         <v>6880000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6960000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7013000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7432000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3493000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2055000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2107000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2007000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3654000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3738000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3776000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>27439000</v>
+        <v>22383000</v>
       </c>
       <c r="E49" s="3">
+        <v>22443000</v>
+      </c>
+      <c r="F49" s="3">
         <v>34443000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32139000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29454000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29926000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11698000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11385000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11544000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10114000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8723000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8999000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8777000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14755000</v>
+        <v>16504000</v>
       </c>
       <c r="E52" s="3">
+        <v>14987000</v>
+      </c>
+      <c r="F52" s="3">
         <v>12969000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13858000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11888000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13428000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6106000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12698000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>90000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>75000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>531176000</v>
+      </c>
+      <c r="E54" s="3">
         <v>535349000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>555255000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>541241000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>509228000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>473078000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>225697000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>221642000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>219276000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>209947000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>186834000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>183010000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>184499000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,77 +2654,81 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>390524000</v>
+      </c>
+      <c r="E57" s="3">
         <v>395865000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>413495000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>416488000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>381077000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>334727000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>161199000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>161989000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5745000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6066000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12514000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14037000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8223000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>27726000</v>
+        <v>33526000</v>
       </c>
       <c r="E58" s="3">
+        <v>31595000</v>
+      </c>
+      <c r="F58" s="3">
         <v>26393000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5878000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6647000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18974000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5425000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5652000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2605,20 +2738,23 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
+      <c r="E59" s="3">
+        <v>3539000</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>5</v>
@@ -2647,39 +2783,42 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>423591000</v>
+        <v>424050000</v>
       </c>
       <c r="E60" s="3">
+        <v>430999000</v>
+      </c>
+      <c r="F60" s="3">
         <v>439888000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>422366000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>387724000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>353701000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>166624000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>167641000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>40025000</v>
+        <v>34222000</v>
       </c>
       <c r="E61" s="3">
+        <v>36135000</v>
+      </c>
+      <c r="F61" s="3">
         <v>44748000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37513000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41493000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>43070000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23709000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23648000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17847000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18037000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23312000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21493000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19114000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11821000</v>
+        <v>8660000</v>
       </c>
       <c r="E62" s="3">
+        <v>8303000</v>
+      </c>
+      <c r="F62" s="3">
         <v>9427000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11121000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7865000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8180000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4699000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>119000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>55000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>262000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>153000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>467497000</v>
+      </c>
+      <c r="E66" s="3">
         <v>476096000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>494718000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>471970000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>438316000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>406520000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>195519000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>191947000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>189395000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>182641000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>162545000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>160251000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>163341000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,14 +3210,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>6673000</v>
+        <v>5907000</v>
       </c>
       <c r="E70" s="3">
         <v>6673000</v>
@@ -3062,13 +3229,13 @@
         <v>6673000</v>
       </c>
       <c r="G70" s="3">
+        <v>6673000</v>
+      </c>
+      <c r="H70" s="3">
         <v>8048000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>5102000</v>
-      </c>
-      <c r="I70" s="3">
-        <v>3053000</v>
       </c>
       <c r="J70" s="3">
         <v>3053000</v>
@@ -3077,20 +3244,23 @@
         <v>3053000</v>
       </c>
       <c r="L70" s="3">
-        <v>2603000</v>
+        <v>3053000</v>
       </c>
       <c r="M70" s="3">
         <v>2603000</v>
       </c>
       <c r="N70" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="O70" s="3">
         <v>5206000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>2116000</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23777000</v>
+      </c>
+      <c r="E72" s="3">
         <v>22088000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26264000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22998000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19455000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19806000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18118000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16259000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14809000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13464000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12317000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11044000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10129000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57772000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52428000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53841000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>62598000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>62759000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61282000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27069000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26595000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26828000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24703000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21686000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17553000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19042000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4818000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1091000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6260000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6440000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4482000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3224000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3237000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2394000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2259000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1936000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1983000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1563000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1916000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>613000</v>
+      </c>
+      <c r="E83" s="3">
         <v>688000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>783000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>810000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>923000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>466000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>424000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>408000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>555000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>461000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>424000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>421000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>391000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2164000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8631000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11081000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7892000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7437000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1520000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4349000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4635000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3115000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3131000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3210000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5308000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3714000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,32 +4021,33 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4673000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1638000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3254000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-224000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-363000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
@@ -3837,15 +4057,18 @@
       <c r="M91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-145000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18598000</v>
+      </c>
+      <c r="E94" s="3">
         <v>22858000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29972000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32056000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43652000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>8348000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4963000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5410000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-976000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1849000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4015000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7047000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3997,41 +4230,44 @@
         <v>2770000</v>
       </c>
       <c r="E96" s="3">
+        <v>2770000</v>
+      </c>
+      <c r="F96" s="3">
         <v>2656000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2485000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2424000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1309000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1169300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1005000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1092000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-937000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-814000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-912000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-564000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11638000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22266000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20017000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>25591000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>36018000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5353000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1502000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-549000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1882000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>104000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>965000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1973000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2796000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4224,8 +4472,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4239,49 +4487,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9124000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9223000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1126000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1427000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-197000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15221000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>888000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1324000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>257000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1386000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>160000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-874000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-537000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>TFC</t>
   </si>
@@ -656,117 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18425000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11408000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17913000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19196000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23109000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20370000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11953000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10992000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10770000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7066000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6327000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6142000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6507000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6917000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,39 +815,42 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18425000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11408000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17913000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19196000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23109000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20370000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11953000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10992000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10770000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,39 +979,42 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>120000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6398000</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
+        <v>6078000</v>
+      </c>
+      <c r="G14" s="3">
         <v>466000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>822000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>860000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>360000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>146000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>507000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1008,54 +1027,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>814000</v>
+        <v>837000</v>
       </c>
       <c r="E15" s="3">
-        <v>908000</v>
+        <v>958000</v>
       </c>
       <c r="F15" s="3">
+        <v>1083000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1054000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1194000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1350000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>494000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>435000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>430000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-150000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-105000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-91000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-106000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11200000</v>
+        <v>11623000</v>
       </c>
       <c r="E17" s="3">
-        <v>11061000</v>
+        <v>11320000</v>
       </c>
       <c r="F17" s="3">
+        <v>11381000</v>
+      </c>
+      <c r="G17" s="3">
         <v>11063000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13583000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13227000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7329000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6521000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6642000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1317000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1163000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1019000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1483000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2117000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>208000</v>
+        <v>6802000</v>
       </c>
       <c r="E18" s="3">
-        <v>6852000</v>
+        <v>88000</v>
       </c>
       <c r="F18" s="3">
+        <v>6532000</v>
+      </c>
+      <c r="G18" s="3">
         <v>8133000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9526000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7143000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4624000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4471000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4128000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5749000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5164000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5123000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5024000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4800000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,98 +1211,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>453000</v>
+      </c>
+      <c r="E20" s="3">
         <v>689000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1219000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>638000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>711000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>810000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>245000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>265000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>295000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2249000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2247000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1996000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1741000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2008000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>333000</v>
+        <v>7186000</v>
       </c>
       <c r="E21" s="3">
-        <v>6541000</v>
+        <v>357000</v>
       </c>
       <c r="F21" s="3">
+        <v>6396000</v>
+      </c>
+      <c r="G21" s="3">
         <v>8549000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10009000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7683000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4873000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4641000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4263000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4055000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3378000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3551000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3704000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3183000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1337,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6349000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-601000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-765000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7029000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7993000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5473000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4019000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4060000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3326000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2917000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3127000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3283000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2792000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1042000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-556000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>738000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1250000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1556000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>981000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>782000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>803000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>911000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1058000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>794000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>921000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1553000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>764000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5307000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1503000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5779000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6437000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4492000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3237000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3257000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2415000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2442000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2123000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2206000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1730000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2028000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4974000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4469000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1452000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5927000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6033000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4184000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3028000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3063000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2220000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2259000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1936000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1983000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1563000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,24 +1640,27 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>4863000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>412000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>481000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-689000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1219000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-638000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-711000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-810000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-245000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-265000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-295000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2249000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2247000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1996000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1741000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2008000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5307000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4818000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1091000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6260000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6440000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4482000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3224000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3237000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2394000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2259000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1936000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1983000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1563000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5307000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4818000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1091000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6260000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6440000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4482000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3224000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3237000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2394000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2259000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1936000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1983000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1563000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,127 +2072,134 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36377000</v>
+      </c>
+      <c r="E41" s="3">
         <v>39768000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30230000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21421000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20295000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18868000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19065000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3844000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2713000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1897000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2123000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1639000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1565000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2011000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10333000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8616000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7661000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8770000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10821000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9454000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9203000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>783000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1076000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2089000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1646000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1294000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1418000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2519000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1904000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>997000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2682000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2244000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1833000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2418000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1116000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2121,39 +2213,42 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>48000</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>57000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>51000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>52000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>123000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>63000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>57000</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2166,38 +2261,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2028000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2069000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9740000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2265000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1791000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1934000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1807000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>745000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2211,39 +2309,42 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>54854000</v>
+        <v>53320000</v>
       </c>
       <c r="E46" s="3">
+        <v>54806000</v>
+      </c>
+      <c r="F46" s="3">
         <v>51048000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37806000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41166000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39447000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42243000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8141000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5315000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2256,39 +2357,42 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>123631000</v>
+      </c>
+      <c r="E47" s="3">
         <v>128372000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>130569000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>138516000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>162040000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>127527000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>81756000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48804000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47978000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5576000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5592000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6002000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6880000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6960000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7013000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7432000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3493000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2055000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2107000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2007000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3654000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3738000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3776000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22353000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22383000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22443000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34443000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32139000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29454000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29926000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11698000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11385000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11544000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10114000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8723000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8999000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8777000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16504000</v>
+        <v>17586000</v>
       </c>
       <c r="E52" s="3">
+        <v>16552000</v>
+      </c>
+      <c r="F52" s="3">
         <v>14987000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12969000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13858000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11888000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13428000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6106000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12698000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>90000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>75000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>547538000</v>
+      </c>
+      <c r="E54" s="3">
         <v>531176000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>535349000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>555255000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>541241000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>509228000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>473078000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>225697000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>221642000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>219276000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>209947000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>186834000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>183010000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>184499000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,83 +2784,87 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400398000</v>
+      </c>
+      <c r="E57" s="3">
         <v>390524000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>395865000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>413495000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>416488000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>381077000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>334727000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>161199000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>161989000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5745000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6066000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12514000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14037000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8223000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>33526000</v>
+        <v>34382000</v>
       </c>
       <c r="E58" s="3">
+        <v>33235000</v>
+      </c>
+      <c r="F58" s="3">
         <v>31595000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>26393000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5878000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6647000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18974000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5425000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5652000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2741,24 +2874,27 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
         <v>3539000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2786,42 +2922,45 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>424050000</v>
+        <v>434780000</v>
       </c>
       <c r="E60" s="3">
+        <v>423759000</v>
+      </c>
+      <c r="F60" s="3">
         <v>430999000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>439888000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>422366000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>387724000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>353701000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>166624000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>167641000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>34222000</v>
+        <v>38493000</v>
       </c>
       <c r="E61" s="3">
+        <v>34513000</v>
+      </c>
+      <c r="F61" s="3">
         <v>36135000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44748000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37513000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41493000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43070000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23709000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23648000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17847000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18037000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23312000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21493000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19114000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8447000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8660000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8303000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9427000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11121000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7865000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8180000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4699000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>119000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>55000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>262000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>153000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>482349000</v>
+      </c>
+      <c r="E66" s="3">
         <v>467497000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>476096000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>494718000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>471970000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>438316000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>406520000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>195519000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>191947000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>189395000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>182641000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>162545000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>160251000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>163341000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,17 +3377,20 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>4916000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5907000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>6673000</v>
       </c>
       <c r="F70" s="3">
         <v>6673000</v>
@@ -3232,13 +3399,13 @@
         <v>6673000</v>
       </c>
       <c r="H70" s="3">
+        <v>6673000</v>
+      </c>
+      <c r="I70" s="3">
         <v>8048000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>5102000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>3053000</v>
       </c>
       <c r="K70" s="3">
         <v>3053000</v>
@@ -3247,20 +3414,23 @@
         <v>3053000</v>
       </c>
       <c r="M70" s="3">
-        <v>2603000</v>
+        <v>3053000</v>
       </c>
       <c r="N70" s="3">
         <v>2603000</v>
       </c>
       <c r="O70" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="P70" s="3">
         <v>5206000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>2116000</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26067000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23777000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22088000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26264000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22998000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19455000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19806000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18118000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16259000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14809000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13464000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12317000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11044000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10129000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>60273000</v>
+      </c>
+      <c r="E76" s="3">
         <v>57772000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52428000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53841000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>62598000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62759000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61282000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27069000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26595000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26828000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24703000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21686000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17553000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19042000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5307000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4818000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1091000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6260000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6440000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4482000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3224000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3237000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2394000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2259000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1936000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1983000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1563000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>547000</v>
+      </c>
+      <c r="E83" s="3">
         <v>613000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>688000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>783000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>810000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>923000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>466000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>424000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>408000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>555000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>461000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>424000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>421000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>391000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5739000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2164000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8631000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11081000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7892000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7437000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1520000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4349000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4635000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3115000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3131000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3210000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5308000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3714000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,35 +4241,36 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-17000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4673000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1638000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3254000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-224000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-363000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4060,15 +4280,18 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17763000</v>
+      </c>
+      <c r="E94" s="3">
         <v>18598000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>22858000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29972000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-32056000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43652000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8348000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4963000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5410000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-976000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1849000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4015000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7047000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>2770000</v>
+        <v>2672000</v>
       </c>
       <c r="E96" s="3">
         <v>2770000</v>
       </c>
       <c r="F96" s="3">
+        <v>2770000</v>
+      </c>
+      <c r="G96" s="3">
         <v>2656000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2485000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2424000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1309000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1169300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1005000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1092000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-937000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-814000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-912000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-564000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8633000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11638000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22266000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20017000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>25591000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36018000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5353000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1502000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-549000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1882000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>104000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>965000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1973000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2796000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4475,8 +4723,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4490,52 +4738,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3391000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9124000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9223000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1126000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1427000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-197000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15221000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>888000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1324000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>257000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1386000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>160000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-874000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
